--- a/MAJSushiConfig/ig/StructureDefinition-FRLMSpecimen.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMSpecimen.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMSpecimen</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSpecimen</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T10:25:17+00:00</t>
+    <t>2026-09-07T11:26:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -294,8 +294,8 @@
     <t>FRLMSpecimen.specimenSource[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatient
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMLocationhttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDevice</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatient
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMLocationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevice</t>
   </si>
   <si>
     <t>Origine du prélèvement : il peut provenir d'un patient, d'un lieu ou d'un dispositif</t>
@@ -304,7 +304,7 @@
     <t>FRLMSpecimen.parentSpecimen</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMSpecimen
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMSpecimen
 </t>
   </si>
   <si>
@@ -314,7 +314,7 @@
     <t>FRLMSpecimen.request</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMServiceRequest
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMServiceRequest
 </t>
   </si>
   <si>
@@ -343,8 +343,8 @@
     <t>FRLMSpecimen.collection.performer[x]</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMHealthProfessional
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMOrganisationhttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMPatienthttps://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMRelatedPerson</t>
+    <t>https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMHealthProfessional
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMOrganisationhttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMPatienthttps://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMRelatedPerson</t>
   </si>
   <si>
     <t>Organisation prélevante</t>
@@ -382,7 +382,7 @@
     <t>FRLMSpecimen.collection.device</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDeviceUse
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDeviceUse
 </t>
   </si>
   <si>
@@ -393,7 +393,7 @@
   </si>
   <si>
     <t>CodeableConcept
-https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDevice</t>
+https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevice</t>
   </si>
   <si>
     <t>Produit utilisé</t>
@@ -402,7 +402,7 @@
     <t>FRLMSpecimen.collection.bodySite</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMBodyStructure
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMBodyStructure
 </t>
   </si>
   <si>
@@ -434,7 +434,7 @@
     <t>FRLMSpecimen.container.containerDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/metier/document-core/StructureDefinition/FRLMDevice
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document-core/StructureDefinition/FRLMDevice
 </t>
   </si>
   <si>
@@ -772,7 +772,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="218.4921875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="201.41015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>

--- a/MAJSushiConfig/ig/StructureDefinition-FRLMSpecimen.xlsx
+++ b/MAJSushiConfig/ig/StructureDefinition-FRLMSpecimen.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-07T11:26:50+00:00</t>
+    <t>2026-09-07T11:40:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
